--- a/data/trans_dic/IP12B$diarrea-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,25</t>
+          <t>0,0; 34,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 29,58</t>
+          <t>3,43; 28,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,88</t>
+          <t>0,0; 31,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,41</t>
+          <t>0,0; 43,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 48,0</t>
+          <t>6,79; 47,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 31,71</t>
+          <t>3,45; 28,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 30,27</t>
+          <t>6,5; 29,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,5</t>
+          <t>0,0; 22,21</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 26,41</t>
+          <t>3,14; 26,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 27,5</t>
+          <t>3,15; 28,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,68</t>
+          <t>0,0; 13,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,07</t>
+          <t>0,0; 18,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,6</t>
+          <t>0,0; 19,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 29,38</t>
+          <t>3,52; 27,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 15,6</t>
+          <t>1,77; 16,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 18,44</t>
+          <t>2,9; 17,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 14,44</t>
+          <t>1,75; 14,77</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,62</t>
+          <t>0,0; 23,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,1</t>
+          <t>0,0; 21,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,47</t>
+          <t>0,0; 23,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,34</t>
+          <t>0,0; 14,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,14</t>
+          <t>0,0; 16,35</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,48</t>
+          <t>0,0; 43,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,25</t>
+          <t>0,0; 50,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 31,28</t>
+          <t>4,03; 31,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,47</t>
+          <t>0,0; 25,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 19,61</t>
+          <t>2,49; 20,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,86</t>
+          <t>0,0; 28,04</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 16,44</t>
+          <t>3,53; 15,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 14,81</t>
+          <t>3,11; 14,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 13,5</t>
+          <t>2,23; 13,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 15,5</t>
+          <t>2,82; 15,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 18,66</t>
+          <t>5,23; 18,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 13,32</t>
+          <t>1,56; 14,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 12,7</t>
+          <t>3,87; 12,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,81</t>
+          <t>5,16; 13,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,29</t>
+          <t>3,25; 11,17</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2562</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5163</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3179</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>615; 5191</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3736</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>898; 6294</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>637; 5322</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2029; 9204</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4279</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1678</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2112</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1612</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3724</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2631</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>504; 4249</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>638; 5713</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2959</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4993</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>643; 4954</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>631; 5736</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1316; 7820</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>715; 6052</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2483</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2629</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3308</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3005</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4263</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3716</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3909</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>604; 4742</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3935</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>600; 5024</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4677</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3679</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10792</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6486</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1551; 6800</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1903; 8644</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1229; 7367</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1315; 7394</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3324; 11862</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>748; 6722</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3509; 11239</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>6442; 17051</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3348; 11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$diarrea-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,82</t>
+          <t>0,0; 34,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 28,89</t>
+          <t>3,5; 28,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,49</t>
+          <t>0,0; 30,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,73</t>
+          <t>0,0; 42,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 47,56</t>
+          <t>6,94; 50,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 28,84</t>
+          <t>3,33; 30,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,5; 29,5</t>
+          <t>6,99; 30,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,21</t>
+          <t>0,0; 19,37</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 26,46</t>
+          <t>3,12; 28,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 28,23</t>
+          <t>3,13; 28,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,02</t>
+          <t>0,0; 13,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,31</t>
+          <t>0,0; 15,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,88</t>
+          <t>0,0; 19,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 27,15</t>
+          <t>3,43; 27,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,08</t>
+          <t>1,76; 15,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 17,24</t>
+          <t>3,11; 17,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 14,77</t>
+          <t>1,59; 14,43</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,11</t>
+          <t>0,0; 21,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,86</t>
+          <t>0,0; 22,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,56</t>
+          <t>0,0; 27,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,51</t>
+          <t>0,0; 13,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,35</t>
+          <t>0,0; 17,45</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,67</t>
+          <t>0,0; 49,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,16</t>
+          <t>0,0; 50,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 31,64</t>
+          <t>3,91; 30,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,0</t>
+          <t>0,0; 25,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 20,88</t>
+          <t>2,45; 21,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,04</t>
+          <t>0,0; 23,62</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 15,5</t>
+          <t>2,65; 15,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,1</t>
+          <t>2,58; 13,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 13,36</t>
+          <t>3,05; 14,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 15,83</t>
+          <t>2,83; 14,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 18,66</t>
+          <t>4,84; 17,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 14,05</t>
+          <t>1,58; 13,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 12,41</t>
+          <t>4,04; 12,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 13,66</t>
+          <t>5,23; 13,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,17</t>
+          <t>3,19; 10,73</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,27 +1417,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3179</t>
+          <t>0; 3139</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>615; 5191</t>
+          <t>628; 5192</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3736</t>
+          <t>0; 3650</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4077</t>
+          <t>0; 3954</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>898; 6294</t>
+          <t>919; 6669</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>637; 5322</t>
+          <t>615; 5624</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2029; 9204</t>
+          <t>2179; 9360</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4279</t>
+          <t>0; 3730</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>504; 4249</t>
+          <t>501; 4555</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>638; 5713</t>
+          <t>634; 5727</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2959</t>
+          <t>0; 2998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3592</t>
+          <t>0; 2948</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4993</t>
+          <t>0; 4967</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>643; 4954</t>
+          <t>626; 4975</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>631; 5736</t>
+          <t>629; 5382</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1316; 7820</t>
+          <t>1409; 8045</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>715; 6052</t>
+          <t>651; 5912</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2483</t>
+          <t>0; 2324</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2629</t>
+          <t>0; 2691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3308</t>
+          <t>0; 3837</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3005</t>
+          <t>0; 2843</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4263</t>
+          <t>0; 4550</t>
         </is>
       </c>
     </row>
@@ -1916,17 +1916,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3716</t>
+          <t>0; 4172</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3909</t>
+          <t>0; 3903</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>604; 4742</t>
+          <t>586; 4619</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3935</t>
+          <t>0; 3948</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>600; 5024</t>
+          <t>589; 5079</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4677</t>
+          <t>0; 3940</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1551; 6800</t>
+          <t>1161; 6945</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1903; 8644</t>
+          <t>1579; 8390</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1229; 7367</t>
+          <t>1679; 7863</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1315; 7394</t>
+          <t>1320; 6767</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3324; 11862</t>
+          <t>3074; 11413</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>748; 6722</t>
+          <t>755; 6453</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3509; 11239</t>
+          <t>3659; 11402</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6442; 17051</t>
+          <t>6535; 16554</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3348; 11500</t>
+          <t>3286; 11046</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$diarrea-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23,93%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>13,42%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11,11%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10,2%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,33%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,37</t>
+          <t>0,0; 43,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 28,9</t>
+          <t>7,76; 48,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,41</t>
+          <t>0,0; 40,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 50,39</t>
+          <t>3,51; 29,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 30,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 30,47</t>
+          <t>3,53; 31,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 30,0</t>
+          <t>7,13; 30,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,37</t>
+          <t>0,0; 21,5</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>10,45%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>10,43%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,57%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 28,37</t>
+          <t>0,0; 18,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 28,29</t>
+          <t>0,0; 21,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,19</t>
+          <t>3,48; 29,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,03</t>
+          <t>3,04; 26,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,77</t>
+          <t>3,11; 27,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 27,26</t>
+          <t>0,0; 10,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,09</t>
+          <t>1,48; 15,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 17,74</t>
+          <t>3,22; 18,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 14,43</t>
+          <t>1,73; 14,44</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,9%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,13%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,37 +908,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,37</t>
+          <t>0,0; 27,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 21,62</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 22,1</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 13,34</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 27,32</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,73</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,45</t>
+          <t>0,0; 16,14</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14,91%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 50,25</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3,97; 31,28</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 49,03</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 50,09</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 30,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 46,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,09</t>
+          <t>0,0; 25,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 21,11</t>
+          <t>2,47; 19,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,62</t>
+          <t>0,0; 26,86</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>6,7%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,67%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 15,83</t>
+          <t>2,8; 15,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 13,69</t>
+          <t>4,42; 18,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 14,26</t>
+          <t>1,61; 13,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,49</t>
+          <t>3,47; 16,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 17,96</t>
+          <t>2,43; 14,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 13,48</t>
+          <t>2,55; 13,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,59</t>
+          <t>4,09; 12,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,26</t>
+          <t>5,33; 13,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 10,73</t>
+          <t>3,23; 11,29</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,27 +1316,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1225</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1210</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1336</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3167</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3139</t>
+          <t>0; 4048</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>628; 5192</t>
+          <t>1027; 6352</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3650</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3954</t>
+          <t>0; 3676</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>919; 6669</t>
+          <t>630; 5314</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3664</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>615; 5624</t>
+          <t>651; 5852</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2179; 9360</t>
+          <t>2226; 9443</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3730</t>
+          <t>0; 4142</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1612</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1678</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2112</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>583</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1612</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>501; 4555</t>
+          <t>0; 3545</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>634; 5727</t>
+          <t>0; 5425</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2998</t>
+          <t>635; 5362</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2948</t>
+          <t>488; 4242</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4967</t>
+          <t>629; 5566</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>626; 4975</t>
+          <t>0; 2427</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>629; 5382</t>
+          <t>527; 5565</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1409; 8045</t>
+          <t>1460; 8364</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>651; 5912</t>
+          <t>709; 5915</t>
         </is>
       </c>
     </row>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2324</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,37 +1753,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2691</t>
+          <t>0; 3859</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0; 2323</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2658</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2763</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3837</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2843</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4550</t>
+          <t>0; 4208</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1269</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0; 3916</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>595; 4688</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4172</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3903</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>586; 4619</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3955</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3948</t>
+          <t>0; 4008</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>589; 5079</t>
+          <t>593; 4718</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3940</t>
+          <t>0; 4480</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>3430</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>4108</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3679</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6684</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2807</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1161; 6945</t>
+          <t>1308; 7239</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1579; 8390</t>
+          <t>2807; 11859</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1679; 7863</t>
+          <t>772; 6375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1320; 6767</t>
+          <t>1525; 7215</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3074; 11413</t>
+          <t>1487; 9075</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>755; 6453</t>
+          <t>1408; 7444</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3659; 11402</t>
+          <t>3704; 11500</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6535; 16554</t>
+          <t>6653; 17248</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3286; 11046</t>
+          <t>3330; 11631</t>
         </is>
       </c>
     </row>
